--- a/apps/guru/public/templates/practice-question-template.xlsx
+++ b/apps/guru/public/templates/practice-question-template.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Soal Latihan" sheetId="1" r:id="Rf0354bcae4d24897"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Petunjuk" sheetId="2" r:id="Rcfe36e5c8e414a7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Soal Latihan" sheetId="1" r:id="R6e35111858234103"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Petunjuk" sheetId="2" r:id="R70a4e80cd4674dfe"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -313,45 +313,48 @@
         <x:v>topik</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
+        <x:v>kode_topik</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
         <x:v>stimulus_html</x:v>
       </x:c>
-      <x:c r="E1" s="6" t="str">
+      <x:c r="F1" s="6" t="str">
         <x:v>pertanyaan_html</x:v>
       </x:c>
-      <x:c r="F1" s="6" t="str">
+      <x:c r="G1" s="6" t="str">
         <x:v>opsi_a</x:v>
       </x:c>
-      <x:c r="G1" s="6" t="str">
+      <x:c r="H1" s="6" t="str">
         <x:v>opsi_b</x:v>
       </x:c>
-      <x:c r="H1" s="6" t="str">
+      <x:c r="I1" s="6" t="str">
         <x:v>opsi_c</x:v>
       </x:c>
-      <x:c r="I1" s="6" t="str">
+      <x:c r="J1" s="6" t="str">
         <x:v>opsi_d</x:v>
       </x:c>
-      <x:c r="J1" s="6" t="str">
+      <x:c r="K1" s="6" t="str">
         <x:v>opsi_e</x:v>
       </x:c>
-      <x:c r="K1" s="6" t="str">
+      <x:c r="L1" s="6" t="str">
         <x:v>kunci_jawaban</x:v>
       </x:c>
-      <x:c r="L1" s="6" t="str">
+      <x:c r="M1" s="6" t="str">
         <x:v>pembahasan_html</x:v>
       </x:c>
-      <x:c r="M1" s="6" t="str">
+      <x:c r="N1" s="6" t="str">
         <x:v>tingkat_kesulitan</x:v>
       </x:c>
-      <x:c r="N1" s="6" t="str">
+      <x:c r="O1" s="6" t="str">
         <x:v>sistem_penilaian</x:v>
       </x:c>
-      <x:c r="O1" s="6" t="str">
+      <x:c r="P1" s="6" t="str">
         <x:v>bobot</x:v>
       </x:c>
-      <x:c r="P1" s="6" t="str">
+      <x:c r="Q1" s="6" t="str">
         <x:v>urutan_stimulus</x:v>
       </x:c>
-      <x:c r="Q1" s="6" t="str">
+      <x:c r="R1" t="str">
         <x:v>status</x:v>
       </x:c>
     </x:row>
@@ -365,42 +368,45 @@
       <x:c r="C2" s="14" t="str">
         <x:v>Energi</x:v>
       </x:c>
-      <x:c r="D2" s="14" t="str"/>
-      <x:c r="E2" s="14" t="str">
+      <x:c r="D2" s="14" t="str">
+        <x:v>ENERGI</x:v>
+      </x:c>
+      <x:c r="E2" s="14"/>
+      <x:c r="F2" s="14" t="str">
         <x:v>&lt;p&gt;Tuliskan pertanyaan latihan di sini.&lt;/p&gt;</x:v>
       </x:c>
-      <x:c r="F2" s="14" t="str">
+      <x:c r="G2" s="14" t="str">
         <x:v>&lt;p&gt;Opsi A&lt;/p&gt;</x:v>
       </x:c>
-      <x:c r="G2" s="14" t="str">
+      <x:c r="H2" s="14" t="str">
         <x:v>&lt;p&gt;Opsi B&lt;/p&gt;</x:v>
       </x:c>
-      <x:c r="H2" s="14" t="str">
+      <x:c r="I2" s="14" t="str">
         <x:v>&lt;p&gt;Opsi C&lt;/p&gt;</x:v>
       </x:c>
-      <x:c r="I2" s="14" t="str">
+      <x:c r="J2" s="14" t="str">
         <x:v>&lt;p&gt;Opsi D&lt;/p&gt;</x:v>
       </x:c>
-      <x:c r="J2" s="14" t="str"/>
-      <x:c r="K2" s="14" t="str">
+      <x:c r="K2" s="14"/>
+      <x:c r="L2" s="14" t="str">
         <x:v>A</x:v>
       </x:c>
-      <x:c r="L2" s="14" t="str">
+      <x:c r="M2" s="14" t="str">
         <x:v>&lt;p&gt;Tuliskan pembahasan jawaban.&lt;/p&gt;</x:v>
       </x:c>
-      <x:c r="M2" s="14" t="str">
+      <x:c r="N2" s="14" t="str">
         <x:v>Mudah</x:v>
       </x:c>
-      <x:c r="N2" s="14" t="str">
+      <x:c r="O2" s="14" t="str">
         <x:v>EXACT_MATCH</x:v>
-      </x:c>
-      <x:c r="O2" s="14" t="n">
-        <x:v>1</x:v>
       </x:c>
       <x:c r="P2" s="14" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Q2" s="14" t="str">
+      <x:c r="Q2" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R2" t="str">
         <x:v>DRAFT</x:v>
       </x:c>
     </x:row>
@@ -415,43 +421,46 @@
         <x:v>Energi</x:v>
       </x:c>
       <x:c r="D3" s="14" t="str">
+        <x:v>ENERGI</x:v>
+      </x:c>
+      <x:c r="E3" s="14" t="str">
         <x:v>&lt;p&gt;Stimulus opsional.&lt;/p&gt;</x:v>
       </x:c>
-      <x:c r="E3" s="14" t="str">
+      <x:c r="F3" s="14" t="str">
         <x:v>&lt;p&gt;Pilih seluruh pernyataan yang benar.&lt;/p&gt;</x:v>
       </x:c>
-      <x:c r="F3" s="14" t="str">
+      <x:c r="G3" s="14" t="str">
         <x:v>&lt;p&gt;Pernyataan A&lt;/p&gt;</x:v>
       </x:c>
-      <x:c r="G3" s="14" t="str">
+      <x:c r="H3" s="14" t="str">
         <x:v>&lt;p&gt;Pernyataan B&lt;/p&gt;</x:v>
       </x:c>
-      <x:c r="H3" s="14" t="str">
+      <x:c r="I3" s="14" t="str">
         <x:v>&lt;p&gt;Pernyataan C&lt;/p&gt;</x:v>
       </x:c>
-      <x:c r="I3" s="14" t="str">
+      <x:c r="J3" s="14" t="str">
         <x:v>&lt;p&gt;Pernyataan D&lt;/p&gt;</x:v>
       </x:c>
-      <x:c r="J3" s="14" t="str"/>
-      <x:c r="K3" s="14" t="str">
+      <x:c r="K3" s="14"/>
+      <x:c r="L3" s="14" t="str">
         <x:v>A,C</x:v>
       </x:c>
-      <x:c r="L3" s="14" t="str">
+      <x:c r="M3" s="14" t="str">
         <x:v>&lt;p&gt;Tuliskan pembahasan jawaban.&lt;/p&gt;</x:v>
       </x:c>
-      <x:c r="M3" s="14" t="str">
+      <x:c r="N3" s="14" t="str">
         <x:v>Sedang</x:v>
       </x:c>
-      <x:c r="N3" s="14" t="str">
+      <x:c r="O3" s="14" t="str">
         <x:v>PARTIAL_NO_PENALTY</x:v>
       </x:c>
-      <x:c r="O3" s="14" t="n">
+      <x:c r="P3" s="14" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P3" s="14" t="n">
+      <x:c r="Q3" s="14" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="Q3" s="14" t="str">
+      <x:c r="R3" t="str">
         <x:v>DRAFT</x:v>
       </x:c>
     </x:row>
@@ -465,40 +474,43 @@
       <x:c r="C4" s="14" t="str">
         <x:v>Energi</x:v>
       </x:c>
-      <x:c r="D4" s="14" t="str"/>
-      <x:c r="E4" s="14" t="str">
+      <x:c r="D4" s="14" t="str">
+        <x:v>ENERGI</x:v>
+      </x:c>
+      <x:c r="E4" s="14"/>
+      <x:c r="F4" s="14" t="str">
         <x:v>&lt;p&gt;Tentukan benar atau salah.&lt;/p&gt;</x:v>
       </x:c>
-      <x:c r="F4" s="14" t="str">
+      <x:c r="G4" s="14" t="str">
         <x:v>&lt;p&gt;Pernyataan 1&lt;/p&gt;</x:v>
       </x:c>
-      <x:c r="G4" s="14" t="str">
+      <x:c r="H4" s="14" t="str">
         <x:v>&lt;p&gt;Pernyataan 2&lt;/p&gt;</x:v>
       </x:c>
-      <x:c r="H4" s="14" t="str">
+      <x:c r="I4" s="14" t="str">
         <x:v>&lt;p&gt;Pernyataan 3&lt;/p&gt;</x:v>
       </x:c>
-      <x:c r="I4" s="14" t="str"/>
-      <x:c r="J4" s="14" t="str"/>
-      <x:c r="K4" s="14" t="str">
+      <x:c r="J4" s="14"/>
+      <x:c r="K4" s="14"/>
+      <x:c r="L4" s="14" t="str">
         <x:v>B,S,B</x:v>
       </x:c>
-      <x:c r="L4" s="14" t="str">
+      <x:c r="M4" s="14" t="str">
         <x:v>&lt;p&gt;Tuliskan pembahasan jawaban.&lt;/p&gt;</x:v>
       </x:c>
-      <x:c r="M4" s="14" t="str">
+      <x:c r="N4" s="14" t="str">
         <x:v>Sedang</x:v>
       </x:c>
-      <x:c r="N4" s="14" t="str">
+      <x:c r="O4" s="14" t="str">
         <x:v>PARTIAL_NO_PENALTY</x:v>
       </x:c>
-      <x:c r="O4" s="14" t="n">
+      <x:c r="P4" s="14" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="P4" s="14" t="n">
+      <x:c r="Q4" s="14" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="Q4" s="14" t="str">
+      <x:c r="R4" t="str">
         <x:v>DRAFT</x:v>
       </x:c>
     </x:row>
@@ -519,7 +531,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c7a6a6678f9423c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ce4db521a1f4839"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -550,33 +562,41 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="13" t="str">
-        <x:v>Kunci PG</x:v>
+        <x:v>Kode topik</x:v>
       </x:c>
       <x:c r="B3" s="13" t="str">
-        <x:v>Gunakan satu huruf, misalnya A.</x:v>
+        <x:v>Isi kode_topik yang sama dengan kode pada template Topik &amp; Materi agar soal latihan masuk ke topik belajar yang benar.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="13" t="str">
-        <x:v>Kunci kompleks</x:v>
+        <x:v>Kunci PG</x:v>
       </x:c>
       <x:c r="B4" s="13" t="str">
-        <x:v>Pisahkan beberapa jawaban dengan koma, misalnya A,C,D.</x:v>
+        <x:v>Gunakan satu huruf, misalnya A.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="13" t="str">
-        <x:v>Kunci benar-salah</x:v>
+        <x:v>Kunci kompleks</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
-        <x:v>Gunakan B atau S sesuai urutan pernyataan, misalnya B,S,B.</x:v>
+        <x:v>Pisahkan beberapa jawaban dengan koma, misalnya A,C,D.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="13" t="str">
+        <x:v>Kunci benar-salah</x:v>
+      </x:c>
+      <x:c r="B6" s="13" t="str">
+        <x:v>Gunakan B atau S sesuai urutan pernyataan, misalnya B,S,B.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
         <x:v>HTML</x:v>
       </x:c>
-      <x:c r="B6" s="13" t="str">
+      <x:c r="B7" t="str">
         <x:v>Kolom berakhiran _html dapat memuat tag sederhana seperti &lt;p&gt;, &lt;strong&gt;, tabel, gambar, dan LaTeX.</x:v>
       </x:c>
     </x:row>
